--- a/output/upload/S00026_1571_연금보험Enterprise_무배당.xlsx
+++ b/output/upload/S00026_1571_연금보험Enterprise_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1571618</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1571618</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>1571618</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>1571618</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
